--- a/数据表/Datas/EntityConfig_实体配置.xlsx
+++ b/数据表/Datas/EntityConfig_实体配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -98,7 +98,16 @@
     </r>
   </si>
   <si>
+    <t>ItemEntity</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -131,6 +140,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -157,6 +172,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -180,6 +201,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -406,13 +433,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF202020"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -955,7 +982,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -974,6 +1001,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1447,7 +1477,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.35" style="1" customWidth="1"/>
@@ -1505,163 +1535,177 @@
       <c r="B5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
+      <c r="C6" s="1" t="str">
+        <f>B6&amp;".prefab"</f>
+        <v>ItemEntity.prefab</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
       <c r="A7" s="7"/>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C7" s="1" t="str">
-        <f t="shared" ref="C7:C11" si="0">B$6&amp;"/"&amp;B7&amp;".prefab"</f>
-        <v>ResourcePoint/ResourcePoint1.prefab</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ResourcePoint/ResourcePoint2.prefab</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ResourcePoint/ResourcePoint3.prefab</v>
+        <f t="shared" ref="C9:C13" si="0">B$8&amp;"/"&amp;B9&amp;".prefab"</f>
+        <v>ResourcePoint/ResourcePoint1.prefab</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:3">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ResourcePoint/ResourcePoint4.prefab</v>
+        <v>ResourcePoint/ResourcePoint2.prefab</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ResourcePoint/ResourcePoint5.prefab</v>
+        <v>ResourcePoint/ResourcePoint3.prefab</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:3">
       <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ResourcePoint/ResourcePoint4.prefab</v>
+      </c>
     </row>
     <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ResourcePoint/ResourcePoint5.prefab</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:3">
-      <c r="B14" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="1" t="str">
-        <f t="shared" ref="C14:C16" si="1">B$13&amp;"/"&amp;B14&amp;".prefab"</f>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="B16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f t="shared" ref="C16:C18" si="1">B$15&amp;"/"&amp;B16&amp;".prefab"</f>
         <v>EnemyUnit/EnemyPartyLowThreat.prefab</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1" t="str">
+    <row r="17" customHeight="1" spans="1:3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EnemyUnit/EnemyPartyMiddleThreat.prefab</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="1" t="str">
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EnemyUnit/EnemyPartyHighThreat.prefab</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="7" t="s">
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="B19" s="7" t="s">
+      <c r="B20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="1" t="str">
-        <f>B$18&amp;"/"&amp;B19&amp;".prefab"</f>
+    </row>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="B21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f>B$20&amp;"/"&amp;B21&amp;".prefab"</f>
         <v>Character/CharacterLeader.prefab</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="1" t="str">
-        <f>B$18&amp;"/"&amp;B20&amp;".prefab"</f>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <f>B$20&amp;"/"&amp;B22&amp;".prefab"</f>
         <v>Character/CharacterRetinue.prefab</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:3">
       <c r="A23" s="7"/>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="1" t="str">
-        <f>B$22&amp;"/"&amp;B23&amp;".prefab"</f>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <f>B$24&amp;"/"&amp;B25&amp;".prefab"</f>
         <v>Map/EvacuatePoint.prefab</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="B24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="1" t="str">
-        <f>B$22&amp;"/"&amp;B24&amp;".prefab"</f>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="B26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <f>B$24&amp;"/"&amp;B26&amp;".prefab"</f>
         <v>Map/MainCamera.prefab</v>
       </c>
     </row>

--- a/数据表/Datas/EntityConfig_实体配置.xlsx
+++ b/数据表/Datas/EntityConfig_实体配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>ItemEntity</t>
+  </si>
+  <si>
+    <t>WorldFloatText</t>
   </si>
   <si>
     <r>
@@ -1477,7 +1480,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.35" style="1" customWidth="1"/>
@@ -1546,24 +1549,23 @@
     </row>
     <row r="7" customHeight="1" spans="1:3">
       <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>B7&amp;".prefab"</f>
+        <v>WorldFloatText.prefab</v>
+      </c>
     </row>
     <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" s="1" t="str">
-        <f t="shared" ref="C9:C13" si="0">B$8&amp;"/"&amp;B9&amp;".prefab"</f>
-        <v>ResourcePoint/ResourcePoint1.prefab</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:3">
@@ -1572,8 +1574,8 @@
         <v>14</v>
       </c>
       <c r="C10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ResourcePoint/ResourcePoint2.prefab</v>
+        <f t="shared" ref="C10:C14" si="0">B$9&amp;"/"&amp;B10&amp;".prefab"</f>
+        <v>ResourcePoint/ResourcePoint1.prefab</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
@@ -1583,7 +1585,7 @@
       </c>
       <c r="C11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ResourcePoint/ResourcePoint3.prefab</v>
+        <v>ResourcePoint/ResourcePoint2.prefab</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:3">
@@ -1593,7 +1595,7 @@
       </c>
       <c r="C12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ResourcePoint/ResourcePoint4.prefab</v>
+        <v>ResourcePoint/ResourcePoint3.prefab</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:3">
@@ -1603,38 +1605,38 @@
       </c>
       <c r="C13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>ResourcePoint/ResourcePoint5.prefab</v>
+        <v>ResourcePoint/ResourcePoint4.prefab</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
       <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>ResourcePoint/ResourcePoint5.prefab</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:3">
       <c r="B16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="1" t="str">
-        <f t="shared" ref="C16:C18" si="1">B$15&amp;"/"&amp;B16&amp;".prefab"</f>
-        <v>EnemyUnit/EnemyPartyLowThreat.prefab</v>
-      </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>EnemyUnit/EnemyPartyMiddleThreat.prefab</v>
+        <f t="shared" ref="C17:C19" si="1">B$16&amp;"/"&amp;B17&amp;".prefab"</f>
+        <v>EnemyUnit/EnemyPartyLowThreat.prefab</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -1644,68 +1646,78 @@
       </c>
       <c r="C18" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>EnemyUnit/EnemyPartyHighThreat.prefab</v>
+        <v>EnemyUnit/EnemyPartyMiddleThreat.prefab</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
       <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="B19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>EnemyUnit/EnemyPartyHighThreat.prefab</v>
+      </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:3">
       <c r="B21" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="1" t="str">
-        <f>B$20&amp;"/"&amp;B21&amp;".prefab"</f>
-        <v>Character/CharacterLeader.prefab</v>
-      </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="1" t="str">
-        <f>B$20&amp;"/"&amp;B22&amp;".prefab"</f>
-        <v>Character/CharacterRetinue.prefab</v>
+        <f>B$21&amp;"/"&amp;B22&amp;".prefab"</f>
+        <v>Character/CharacterLeader.prefab</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:3">
       <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
+      <c r="B23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <f>B$21&amp;"/"&amp;B23&amp;".prefab"</f>
+        <v>Character/CharacterRetinue.prefab</v>
+      </c>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="1" t="str">
-        <f>B$24&amp;"/"&amp;B25&amp;".prefab"</f>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <f>B$25&amp;"/"&amp;B26&amp;".prefab"</f>
         <v>Map/EvacuatePoint.prefab</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="B26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="1" t="str">
-        <f>B$24&amp;"/"&amp;B26&amp;".prefab"</f>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="B27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <f>B$25&amp;"/"&amp;B27&amp;".prefab"</f>
         <v>Map/MainCamera.prefab</v>
       </c>
     </row>

--- a/数据表/Datas/EntityConfig_实体配置.xlsx
+++ b/数据表/Datas/EntityConfig_实体配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -62,7 +62,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>资源名称</t>
@@ -73,7 +73,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>资源路径（相较于</t>
@@ -91,7 +91,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -107,17 +107,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>资源点</t>
@@ -145,17 +135,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -177,17 +157,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>玩家</t>
@@ -206,17 +176,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>地图</t>
@@ -436,14 +396,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="宋体"/>
+      <color rgb="FF9C0006"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1562,9 +1521,12 @@
     </row>
     <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1574,7 +1536,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="1" t="str">
-        <f t="shared" ref="C10:C14" si="0">B$9&amp;"/"&amp;B10&amp;".prefab"</f>
+        <f t="shared" ref="C10:C14" si="0">C$9&amp;"/"&amp;B10&amp;".prefab"</f>
         <v>ResourcePoint/ResourcePoint1.prefab</v>
       </c>
     </row>
@@ -1624,9 +1586,12 @@
     </row>
     <row r="16" customHeight="1" spans="1:3">
       <c r="A16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1635,7 +1600,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="1" t="str">
-        <f t="shared" ref="C17:C19" si="1">B$16&amp;"/"&amp;B17&amp;".prefab"</f>
+        <f t="shared" ref="C17:C19" si="1">C$16&amp;"/"&amp;B17&amp;".prefab"</f>
         <v>EnemyUnit/EnemyPartyLowThreat.prefab</v>
       </c>
     </row>
@@ -1665,9 +1630,12 @@
     </row>
     <row r="21" customHeight="1" spans="1:3">
       <c r="A21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1676,7 +1644,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="1" t="str">
-        <f>B$21&amp;"/"&amp;B22&amp;".prefab"</f>
+        <f>C$21&amp;"/"&amp;B22&amp;".prefab"</f>
         <v>Character/CharacterLeader.prefab</v>
       </c>
     </row>
@@ -1686,7 +1654,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="1" t="str">
-        <f>B$21&amp;"/"&amp;B23&amp;".prefab"</f>
+        <f>C$21&amp;"/"&amp;B23&amp;".prefab"</f>
         <v>Character/CharacterRetinue.prefab</v>
       </c>
     </row>
@@ -1696,9 +1664,12 @@
     </row>
     <row r="25" customHeight="1" spans="1:3">
       <c r="A25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1708,7 +1679,7 @@
         <v>30</v>
       </c>
       <c r="C26" s="1" t="str">
-        <f>B$25&amp;"/"&amp;B26&amp;".prefab"</f>
+        <f>C$25&amp;"/"&amp;B26&amp;".prefab"</f>
         <v>Map/EvacuatePoint.prefab</v>
       </c>
     </row>
@@ -1717,7 +1688,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="1" t="str">
-        <f>B$25&amp;"/"&amp;B27&amp;".prefab"</f>
+        <f>C$25&amp;"/"&amp;B27&amp;".prefab"</f>
         <v>Map/MainCamera.prefab</v>
       </c>
     </row>
